--- a/PEGADA_CARBONO_BASELINE_2026.xlsx
+++ b/PEGADA_CARBONO_BASELINE_2026.xlsx
@@ -61,7 +61,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AB50"/>
+  <dimension ref="A1:AB86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.0" customWidth="true"/>
@@ -243,16 +243,16 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46156.0</v>
+        <v>46196.0</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -267,7 +267,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cosme Militão</t>
+          <t>Atija Baltazar Duarte</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -282,12 +282,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>AMELIA AFUSSA ANTONIO</t>
+          <t>Admira Fernando Tocoto</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,4.	Gás,5.	Carvão,7.	Pilhas / baterias,8.	Combustível (gasolina, diesel, petróleo)</t>
+          <t>1.	Eletricidade da rede,5.	Carvão</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -297,17 +297,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1.	Todos os dias.</t>
+          <t>2.	Algumas vezes por semana.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Às vezes</t>
+          <t>Sempre</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+          <t>Desligo os equipamentos,Tiro os aparelhos da tomada</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -327,7 +327,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Embalagens de papel ou cartão,Embalagens de plástico</t>
+          <t>Embalagens de plástico,Embalagens biodegradaveis/compostáveis</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -352,27 +352,27 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+          <t>As vezes utiliza o lixo orgânico para a compostagem.</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>As vezes vende o lixo orgânico para compostagem.</t>
+          <t>Nunca o lixo orgânico para compostagem</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46157.0</v>
+        <v>46197.0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -392,7 +392,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -407,7 +407,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Faizela  Carlos</t>
+          <t>Atija Baltazar Duarte</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -422,12 +422,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ANCHA FRANCISCO LIMA</t>
+          <t>Alice Gungulo</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,5.	Carvão</t>
+          <t>1.	Eletricidade da rede</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -447,12 +447,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Apago o fogão / carvão / lenha / gerador</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dentro da cidade (mas fora do bairro)</t>
+          <t>Compra dentro do meu bairro.</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -462,12 +462,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Compra sempre que precisa.</t>
+          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Embalagens de plástico</t>
+          <t>Embalagens de papel ou cartão,Embalagens de plástico</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -487,12 +487,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46157.0</v>
+        <v>46156.0</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -562,12 +562,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ANDREA DE FATIMA COUTO MARIO</t>
+          <t>AMELIA AFUSSA ANTONIO</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,3.	Painel solar / energia solar,5.	Carvão</t>
+          <t>1.	Eletricidade da rede,4.	Gás,5.	Carvão,7.	Pilhas / baterias,8.	Combustível (gasolina, diesel, petróleo)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Sempre</t>
+          <t>Às vezes</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -602,12 +602,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Compra sempre que precisa.</t>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>O meu negócio não utiliza embalagens</t>
+          <t>Embalagens de papel ou cartão,Embalagens de plástico</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -627,12 +627,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Nunca o lixo orgânico para compostagem</t>
+          <t>As vezes vende o lixo orgânico para compostagem.</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46156.0</v>
+        <v>46196.0</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Faizela  Carlos</t>
+          <t>Karina Sissa Machava</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AQUILAY JOAO HOVASE</t>
+          <t>Amelia Nhamadjavo Mauricio</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>5.	Carvão</t>
+          <t>1.	Eletricidade da rede,10. Outro</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t/>
+          <t>Vela para queimar as trancas</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>4.	Raramente</t>
+          <t>2.	Algumas vezes por semana.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apago o fogão / carvão / lenha / gerador</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dentro da cidade (mas fora do bairro)</t>
+          <t>Compra dentro do meu bairro.</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Compra sempre que precisa.</t>
+          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -767,17 +767,17 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+          <t>As vezes utiliza o lixo orgânico para a compostagem.</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>As vezes reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46154.0</v>
+        <v>46199.0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cosme Militão</t>
+          <t>Karina Sissa Machava</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ARISTINA RABIA JULIO MANUEL</t>
+          <t>Ana Janetth de Menezes Titos</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede</t>
+          <t>5.	Carvão</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -862,32 +862,32 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Sempre</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+          <t>Apago o fogão / carvão / lenha / gerador</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dentro da cidade (mas fora do bairro)</t>
+          <t>Outro</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">Dentro e fora do bairro </t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+          <t>Compra sempre que precisa.</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão,Embalagens biodegradaveis/compostáveis</t>
+          <t>Embalagens de plástico</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -897,27 +897,27 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t/>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>As vezes utiliza o lixo orgânico para a compostagem.</t>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -927,12 +927,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>As vezes reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -943,16 +943,16 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46154.0</v>
+        <v>46199.0</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Faizela  Carlos</t>
+          <t>Anabela Fernardo</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>Ana Moisés Jorge Meque Lunavo</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,5.	Carvão</t>
+          <t>1.	Eletricidade da rede</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Compra dentro do meu bairro.</t>
+          <t>Dentro da cidade (mas fora do bairro)</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
+          <t>Compra sempre que precisa.</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro)</t>
+          <t>O meu negócio não utiliza embalagens</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1047,17 +1047,17 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+          <t>As vezes utiliza o lixo orgânico para a compostagem.</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>As vezes reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1083,11 +1083,11 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46155.0</v>
+        <v>46157.0</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nelton Antonio Duarte</t>
+          <t>Faizela  Carlos</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>BEMVINDA HALIA MARIO</t>
+          <t>ANCHA FRANCISCO LIMA</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2.	Algumas vezes por semana.</t>
+          <t>1.	Todos os dias.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+          <t>Desligo os equipamentos,Apago o fogão / carvão / lenha / gerador</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Embalagens de papel ou cartão,Embalagens de plástico</t>
+          <t>Embalagens de plástico</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1177,22 +1177,22 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t/>
+          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>As vezes reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -1223,11 +1223,11 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46155.0</v>
+        <v>46157.0</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t>ANDREA DE FATIMA COUTO MARIO</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,5.	Carvão,8.	Combustível (gasolina, diesel, petróleo)</t>
+          <t>1.	Eletricidade da rede,3.	Painel solar / energia solar,5.	Carvão</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador,Guardo o combustível ou material de forma segura</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Embalagens de papel ou cartão,Embalagens de plástico,Embalagens biodegradaveis/compostáveis</t>
+          <t>O meu negócio não utiliza embalagens</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46155.0</v>
+        <v>46199.0</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Faizela  Carlos</t>
+          <t>Anabela Fernardo</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>Ângela Antonio Manuel Bene</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,5.	Carvão,6.	Lenha,7.	Pilhas / baterias</t>
+          <t>5.	Carvão,6.	Lenha,9.	Não utiliza energia</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1417,22 +1417,22 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1.	Todos os dias.</t>
+          <t>5.	Nunca</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Sempre</t>
+          <t>Nunca</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Apago o fogão / carvão / lenha / gerador</t>
+          <t>Outro:</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dentro da cidade (mas fora do bairro)</t>
+          <t>Compra dentro do meu bairro.</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1442,12 +1442,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+          <t>Compra sempre que precisa.</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de plástico</t>
+          <t>O meu negócio não utiliza embalagens</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1457,27 +1457,27 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Nunca adquire produtos vendidos em embalagens plásticas.</t>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t/>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Sempre utiliza o lixo orgânico para a compostagem.</t>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1503,16 +1503,16 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46156.0</v>
+        <v>46196.0</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neusa Domingos</t>
+          <t>Karina Sissa Machava</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>CEZALTINA DA GLORIA MATIAS JOAQUIM</t>
+          <t>Ângela Antonio Manuel Bene</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,5.	Carvão</t>
+          <t>9.	Não utiliza energia</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1557,17 +1557,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2.	Algumas vezes por semana.</t>
+          <t>5.	Nunca</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Sempre</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+          <t>Outro:</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro)</t>
+          <t>Embalagens de plástico</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1627,12 +1627,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>As vezes reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>As vezes reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -1643,16 +1643,16 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46154.0</v>
+        <v>46196.0</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cosme Militão</t>
+          <t>Atija Baltazar Duarte</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>DENISE ISILDA MIGUEL TOCOTA</t>
+          <t>Antonia Alberto António</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,3.	Painel solar / energia solar</t>
+          <t>1.	Eletricidade da rede</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2.	Algumas vezes por semana.</t>
+          <t>1.	Todos os dias.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de plástico,Embalagens biodegradaveis/compostáveis</t>
+          <t>O meu negócio não utiliza embalagens</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>As vezes reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -1783,11 +1783,11 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46154.0</v>
+        <v>46156.0</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neusa Domingos</t>
+          <t>Faizela  Carlos</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>DULQUIFAL ASSANE SIMBA</t>
+          <t>AQUILAY JOAO HOVASE</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,5.	Carvão</t>
+          <t>5.	Carvão</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2.	Algumas vezes por semana.</t>
+          <t>4.	Raramente</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador,Guardo o combustível ou material de forma segura</t>
+          <t>Apago o fogão / carvão / lenha / gerador</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Compra dentro do meu bairro.</t>
+          <t>Dentro da cidade (mas fora do bairro)</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+          <t>Compra sempre que precisa.</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro)</t>
+          <t>O meu negócio não utiliza embalagens</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1923,11 +1923,11 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46162.0</v>
+        <v>46154.0</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,4.	Gás</t>
+          <t>1.	Eletricidade da rede</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1.	Todos os dias.</t>
+          <t>2.	Algumas vezes por semana.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador,Guardo o combustível ou material de forma segura</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Embalagens de plástico</t>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão,Embalagens biodegradaveis/compostáveis</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2027,17 +2027,17 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+          <t>As vezes utiliza o lixo orgânico para a compostagem.</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>As vezes reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46155.0</v>
+        <v>46154.0</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cosme Militão</t>
+          <t>Faizela  Carlos</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>ESMERALDA JORGE MURIRIUA</t>
+          <t>ASSINA ABDALA ABDULSATAR</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2.	Algumas vezes por semana.</t>
+          <t>1.	Todos os dias.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador,Guardo o combustível ou material de forma segura</t>
+          <t>Desligo os equipamentos,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dentro da cidade (mas fora do bairro)</t>
+          <t>Compra dentro do meu bairro.</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão</t>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro)</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>As vezes reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46162.0</v>
+        <v>46155.0</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neusa Domingos</t>
+          <t>Nelton Antonio Duarte</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>ESTEFANIA SAMUEL BOLACHA</t>
+          <t>BEMVINDA HALIA MARIO</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1.	Todos os dias.</t>
+          <t>2.	Algumas vezes por semana.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
+          <t>Compra sempre que precisa.</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão</t>
+          <t>Embalagens de papel ou cartão,Embalagens de plástico</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2302,17 +2302,17 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t/>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>As vezes reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46157.0</v>
+        <v>46155.0</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neusa Domingos</t>
+          <t>Cosme Militão</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>FAIZA FERNANDO HENRIQUES</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,4.	Gás,5.	Carvão</t>
+          <t>1.	Eletricidade da rede,5.	Carvão,8.	Combustível (gasolina, diesel, petróleo)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador,Guardo o combustível ou material de forma segura</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2422,12 +2422,12 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
+          <t>Compra sempre que precisa.</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão,Embalagens de plástico</t>
+          <t>Embalagens de papel ou cartão,Embalagens de plástico,Embalagens biodegradaveis/compostáveis</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46155.0</v>
+        <v>46199.0</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neusa Domingos</t>
+          <t>Karina Sissa Machava</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>FATIMA SALVADOR AMADE</t>
+          <t>Bibiana Pedro Dambujo</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>3.	Algumas vezes por mês.</t>
+          <t>1.	Todos os dias.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+          <t>Compra sempre que precisa.</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Embalagens de plástico</t>
+          <t>O meu negócio não utiliza embalagens</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46154.0</v>
+        <v>46197.0</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cosme Militão</t>
+          <t>Atija Baltazar Duarte</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2662,12 +2662,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t>Blessing Fernando Bito Ofice</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,4.	Gás,5.	Carvão</t>
+          <t>1.	Eletricidade da rede,4.	Gás</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Às vezes</t>
+          <t>Sempre</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador,Guardo o combustível ou material de forma segura</t>
+          <t>Desligo os equipamentos,Tiro os aparelhos da tomada</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Embalagens de papel ou cartão,Embalagens de plástico</t>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão,Embalagens de plástico</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2727,17 +2727,17 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Sempre utiliza o lixo orgânico para a compostagem.</t>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>As vezes reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46155.0</v>
+        <v>46196.0</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nelton Antonio Duarte</t>
+          <t>Atija Baltazar Duarte</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>FRANCISCA LUCIANO BOMES</t>
+          <t>Carmen Carlos Nhandoro Vasco</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede</t>
+          <t>9.	Não utiliza energia</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2817,17 +2817,17 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.	Todos os dias.</t>
+          <t>5.	Nunca</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Sempre</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+          <t>Outro:</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Compra sempre que precisa.</t>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>O meu negócio não utiliza embalagens</t>
+          <t>Embalagens de papel ou cartão,Embalagens de plástico</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2887,12 +2887,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>As vezes reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46154.0</v>
+        <v>46155.0</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cosme Militão</t>
+          <t>Faizela  Carlos</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,4.	Gás,5.	Carvão</t>
+          <t>1.	Eletricidade da rede,5.	Carvão,6.	Lenha,7.	Pilhas / baterias</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2.	Algumas vezes por semana.</t>
+          <t>1.	Todos os dias.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador,Guardo o combustível ou material de forma segura</t>
+          <t>Desligo os equipamentos,Apago o fogão / carvão / lenha / gerador</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão,Embalagens de plástico,Embalagens biodegradaveis/compostáveis</t>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de plástico</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+          <t>Nunca adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -3007,17 +3007,17 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+          <t>Sempre utiliza o lixo orgânico para a compostagem.</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>As vezes reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>As vezes reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -3043,16 +3043,16 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46154.0</v>
+        <v>46197.0</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nelton Antonio Duarte</t>
+          <t>Atija Baltazar Duarte</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>Celsa Bartolomeu Januario</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,5.	Carvão,7.	Pilhas / baterias</t>
+          <t>1.	Eletricidade da rede</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador,Deixo ligado porque ainda volto a usar</t>
+          <t>Desligo os equipamentos,Tiro os aparelhos da tomada</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de plástico</t>
+          <t>Embalagens de plástico</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>As vezes reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3183,11 +3183,11 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46162.0</v>
+        <v>46156.0</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nelton Antonio Duarte</t>
+          <t>Neusa Domingos</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>CEZALTINA DA GLORIA MATIAS JOAQUIM</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede</t>
+          <t>1.	Eletricidade da rede,5.	Carvão</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.	Todos os dias.</t>
+          <t>2.	Algumas vezes por semana.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+          <t>Desligo os equipamentos,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>O meu negócio não utiliza embalagens</t>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro)</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>As vezes reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3323,11 +3323,11 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46162.0</v>
+        <v>46154.0</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Compra e venda de produtos não alimentares ( roupa,crédito, etc: sem transformação)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Emilia Xavier</t>
+          <t>Cosme Militão</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>INES BERNARDO</t>
+          <t>DENISE ISILDA MIGUEL TOCOTA</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,3.	Painel solar / energia solar,5.	Carvão</t>
+          <t>1.	Eletricidade da rede,3.	Painel solar / energia solar</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.	Todos os dias.</t>
+          <t>2.	Algumas vezes por semana.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Embalagens de papel ou cartão</t>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de plástico,Embalagens biodegradaveis/compostáveis</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3447,12 +3447,12 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46155.0</v>
+        <v>46199.0</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neusa Domingos</t>
+          <t>Atija Baltazar Duarte</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>ISAURA EVA ABILIO</t>
+          <t>Domingas Jose António</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,5.	Carvão,6.	Lenha</t>
+          <t>5.	Carvão,6.	Lenha</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+          <t>Apago o fogão / carvão / lenha / gerador</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+          <t>Compra sempre que precisa.</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro)</t>
+          <t>Embalagens de plástico</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -3562,17 +3562,17 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t/>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anselma Paulo Sitoe</t>
+          <t>Neusa Domingos</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>IVANDRA CHALES</t>
+          <t>DULQUIFAL ASSANE SIMBA</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede</t>
+          <t>1.	Eletricidade da rede,5.	Carvão</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1.	Todos os dias.</t>
+          <t>2.	Algumas vezes por semana.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador,Guardo o combustível ou material de forma segura</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Dentro da cidade (mas fora do bairro)</t>
+          <t>Compra dentro do meu bairro.</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Embalagens de plástico</t>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro)</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3743,16 +3743,16 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46155.0</v>
+        <v>46196.0</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neusa Domingos</t>
+          <t>Anabela Fernardo</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>Edna Ana João Tapera</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,5.	Carvão,6.	Lenha,8.	Combustível (gasolina, diesel, petróleo)</t>
+          <t>1.	Eletricidade da rede</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2.	Algumas vezes por semana.</t>
+          <t>1.	Todos os dias.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro)</t>
+          <t>O meu negócio não utiliza embalagens</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -3847,17 +3847,17 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Sempre utiliza o lixo orgânico para a compostagem.</t>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>As vezes reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46163.0</v>
+        <v>46162.0</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neusa Domingos</t>
+          <t>Cosme Militão</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,5.	Carvão</t>
+          <t>1.	Eletricidade da rede,4.	Gás</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2.	Algumas vezes por semana.</t>
+          <t>1.	Todos os dias.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+          <t>Desligo os equipamentos,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador,Guardo o combustível ou material de forma segura</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro)</t>
+          <t>Embalagens de plástico</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4023,11 +4023,11 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46154.0</v>
+        <v>46155.0</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Emilia Xavier</t>
+          <t>Cosme Militão</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede</t>
+          <t>1.	Eletricidade da rede,5.	Carvão</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador,Guardo o combustível ou material de forma segura</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>O meu negócio não utiliza embalagens</t>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>Nunca adquire produtos vendidos em embalagens plásticas.</t>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>As vezes reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -4163,11 +4163,11 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46153.0</v>
+        <v>46162.0</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nelton Antonio Duarte</t>
+          <t>Neusa Domingos</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>ESTEFANIA SAMUEL BOLACHA</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede</t>
+          <t>1.	Eletricidade da rede,5.	Carvão</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de plástico</t>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4303,16 +4303,16 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46153.0</v>
+        <v>46197.0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nelton Antonio Duarte</t>
+          <t>Karina Sissa Machava</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>MADALENA CARIM MERAGE</t>
+          <t>Faira Jamal Ibraimo</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,5.	Carvão,6.	Lenha,7.	Pilhas / baterias</t>
+          <t>4.	Gás,5.	Carvão</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1.	Todos os dias.</t>
+          <t>2.	Algumas vezes por semana.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4367,32 +4367,32 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dentro da cidade (mas fora do bairro)</t>
+          <t>Outro</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">Dentro e fora do bairro </t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Compra sempre que precisa.</t>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão,Embalagens de plástico</t>
+          <t>Outro</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">Takes away, take away de aluminio </t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>As vezes reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46163.0</v>
+        <v>46157.0</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Faizela  Carlos</t>
+          <t>Neusa Domingos</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>FAIZA FERNANDO HENRIQUES</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2.	Algumas vezes por semana.</t>
+          <t>1.	Todos os dias.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nelton Antonio Duarte</t>
+          <t>Neusa Domingos</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>MARIAMO  DOMINGOS JAIROSSE</t>
+          <t>FATIMA SALVADOR AMADE</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2.	Gerador,8.	Combustível (gasolina, diesel, petróleo)</t>
+          <t>1.	Eletricidade da rede</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>4.	Raramente</t>
+          <t>3.	Algumas vezes por mês.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Apago o fogão / carvão / lenha / gerador,Guardo o combustível ou material de forma segura</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Compra sempre que precisa.</t>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de plástico,Embalagens biodegradaveis/compostáveis</t>
+          <t>Embalagens de plástico</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>Sempre utiliza o lixo orgânico para a compostagem.</t>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46156.0</v>
+        <v>46154.0</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Emilia Xavier</t>
+          <t>Cosme Militão</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>MARIAMO HANIFA ABACAR CHALE SALIMO</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,5.	Carvão</t>
+          <t>1.	Eletricidade da rede,4.	Gás,5.	Carvão</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Deixo ligado porque ainda volto a usar</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador,Guardo o combustível ou material de forma segura</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fora da cidade.</t>
+          <t>Dentro da cidade (mas fora do bairro)</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro)</t>
+          <t>Embalagens de papel ou cartão,Embalagens de plástico</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Nunca adquire produtos vendidos em embalagens plásticas.</t>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>As vezes vende o lixo orgânico para compostagem.</t>
+          <t>Nunca o lixo orgânico para compostagem</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>As vezes reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -4863,16 +4863,16 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46154.0</v>
+        <v>46197.0</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Faizela  Carlos</t>
+          <t>Anabela Fernardo</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>MIMI IBRAIMO OMAR</t>
+          <t>Florinda Cuambe Manuel Quissico</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Sempre</t>
+          <t>Nunca</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+          <t>Desligo as luzes,Tiro os aparelhos da tomada</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4942,12 +4942,12 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Compra sempre que precisa.</t>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>O meu negócio não utiliza embalagens</t>
+          <t>Embalagens de plástico</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46156.0</v>
+        <v>46155.0</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>NATANIELA DILCIA MASSANGAIE</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+          <t>Compra sempre que precisa.</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -5143,16 +5143,16 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46154.0</v>
+        <v>46199.0</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cosme Militão</t>
+          <t>Atija Baltazar Duarte</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>NGAMO SUMAIL</t>
+          <t>Gina Francisco</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,4.	Gás,7.	Pilhas / baterias</t>
+          <t>1.	Eletricidade da rede</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Guardo o combustível ou material de forma segura</t>
+          <t>Desligo os equipamentos,Tiro os aparelhos da tomada</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Embalagens de papel ou cartão,Embalagens de plástico</t>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão,Embalagens de plástico</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>As vezes reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46157.0</v>
+        <v>46154.0</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nelton Antonio Duarte</t>
+          <t>Cosme Militão</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>OLINDA CARLINDO NAMIRECA</t>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,4.	Gás,5.	Carvão,6.	Lenha</t>
+          <t>1.	Eletricidade da rede,4.	Gás,5.	Carvão</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador,Guardo o combustível ou material de forma segura</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão,Embalagens de plástico</t>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão,Embalagens de plástico,Embalagens biodegradaveis/compostáveis</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -5392,12 +5392,12 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>Sempre utiliza o lixo orgânico para a compostagem.</t>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46155.0</v>
+        <v>46154.0</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Faizela  Carlos</t>
+          <t>Nelton Antonio Duarte</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>OTILIA LUIS</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,5.	Carvão</t>
+          <t>1.	Eletricidade da rede,5.	Carvão,7.	Pilhas / baterias</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2.	Algumas vezes por semana.</t>
+          <t>1.	Todos os dias.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+          <t>Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador,Deixo ligado porque ainda volto a usar</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5502,12 +5502,12 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Compra sempre que precisa.</t>
+          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Embalagens de papel ou cartão,Embalagens de plástico</t>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de plástico</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>As vezes utiliza o lixo orgânico para a compostagem.</t>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>As vezes reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5563,7 +5563,7 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46154.0</v>
+        <v>46162.0</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Faizela  Carlos</t>
+          <t>Nelton Antonio Duarte</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>REGINA MANUEL PASSURI</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Compra sempre que precisa.</t>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>As vezes reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46156.0</v>
+        <v>46196.0</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cosme Militão</t>
+          <t>Anabela Fernardo</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5742,12 +5742,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>ROSA ERNESTO CASIMUCA</t>
+          <t>Hérica Simoco</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,4.	Gás,5.	Carvão</t>
+          <t>1.	Eletricidade da rede</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador,Guardo o combustível ou material de forma segura</t>
+          <t>Desligo os equipamentos,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Embalagens de papel ou cartão,Embalagens de plástico</t>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão,Embalagens de plástico,Embalagens biodegradaveis/compostáveis</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>As vezes utiliza o lixo orgânico para a compostagem.</t>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -5843,7 +5843,7 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46156.0</v>
+        <v>46197.0</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nelton Antonio Duarte</t>
+          <t>Atija Baltazar Duarte</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>SAMIRA COMBO MUHOLE ASSUMANE</t>
+          <t>Icelsa Maria dos Anjos</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede</t>
+          <t>1.	Eletricidade da rede,5.	Carvão</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2.	Algumas vezes por semana.</t>
+          <t>1.	Todos os dias.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Compra sempre que precisa.</t>
+          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Embalagens de papel ou cartão,Embalagens biodegradaveis/compostáveis</t>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de plástico</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -5947,17 +5947,17 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+          <t>As vezes utiliza o lixo orgânico para a compostagem.</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>As vezes reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -5983,11 +5983,11 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46156.0</v>
+        <v>46162.0</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Compra e venda de produtos não alimentares ( roupa,crédito, etc: sem transformação)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neusa Domingos</t>
+          <t>Emilia Xavier</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>SHEILA MACARIO ANTONIO  CUMANRARE</t>
+          <t>INES BERNARDO</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede</t>
+          <t>1.	Eletricidade da rede,3.	Painel solar / energia solar,5.	Carvão</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro)</t>
+          <t>Embalagens de papel ou cartão</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t/>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46154.0</v>
+        <v>46199.0</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nelton Antonio Duarte</t>
+          <t>Karina Sissa Machava</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SHEILA RAIMUNDO ANTUNES</t>
+          <t>Isabel Ricardo Lopes Andrade</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,7.	Pilhas / baterias,8.	Combustível (gasolina, diesel, petróleo)</t>
+          <t>1.	Eletricidade da rede</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>3.	Algumas vezes por mês.</t>
+          <t>1.	Todos os dias.</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Guardo o combustível ou material de forma segura</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Deixo ligado porque ainda volto a usar</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>O meu negócio não utiliza embalagens</t>
+          <t>Embalagens de plástico</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
@@ -6263,11 +6263,11 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46156.0</v>
+        <v>46155.0</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cosme Militão</t>
+          <t>Neusa Domingos</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6302,12 +6302,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>SUZANA JOAQUIM VAQUINA</t>
+          <t>ISAURA EVA ABILIO</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede</t>
+          <t>1.	Eletricidade da rede,5.	Carvão,6.	Lenha</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Guardo o combustível ou material de forma segura</t>
+          <t>Desligo os equipamentos,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Dentro da cidade (mas fora do bairro)</t>
+          <t>Compra dentro do meu bairro.</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Embalagens de plástico</t>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro)</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>As vezes reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -6403,11 +6403,11 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46155.0</v>
+        <v>46154.0</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Neusa Domingos</t>
+          <t>Anselma Paulo Sitoe</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>IVANDRA CHALES</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,5.	Carvão</t>
+          <t>1.	Eletricidade da rede</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -6543,11 +6543,11 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46157.0</v>
+        <v>46155.0</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Faizela  Carlos</t>
+          <t>Neusa Domingos</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>TUCHA OSVALDO FERNANDO</t>
+          <t>JESSICA MARIA JOSE NAMUE</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede</t>
+          <t>1.	Eletricidade da rede,5.	Carvão,6.	Lenha,8.	Combustível (gasolina, diesel, petróleo)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -6597,22 +6597,22 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>4.	Raramente</t>
+          <t>2.	Algumas vezes por semana.</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Nunca</t>
+          <t>Sempre</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Não faço nada em particular</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Compra dentro do meu bairro.</t>
+          <t>Dentro da cidade (mas fora do bairro)</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Compra sempre que precisa.</t>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>O meu negócio não utiliza embalagens</t>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro)</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+          <t>Sempre utiliza o lixo orgânico para a compostagem.</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>As vezes reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
@@ -6683,16 +6683,16 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46156.0</v>
+        <v>46196.0</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Faizela  Carlos</t>
+          <t>Anabela Fernardo</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>VIRGINIA ORLANDO AVELINO</t>
+          <t>Joana Mafato</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,4.	Gás,5.	Carvão</t>
+          <t>1.	Eletricidade da rede</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+          <t>Desligo os equipamentos,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador,Guardo o combustível ou material de forma segura</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Compra sempre que precisa.</t>
+          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>O meu negócio não utiliza embalagens</t>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de plástico,Embalagens biodegradaveis/compostáveis</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -6787,17 +6787,17 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+          <t>Sempre utiliza o lixo orgânico para a compostagem.</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
@@ -6807,12 +6807,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
       </c>
     </row>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46154.0</v>
+        <v>46197.0</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Beira</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Faizela  Carlos</t>
+          <t>Anabela Fernardo</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6862,12 +6862,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>ZIBIA JOAO</t>
+          <t>Joice de Carla Goveia</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1.	Eletricidade da rede,5.	Carvão</t>
+          <t>1.	Eletricidade da rede</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Desligo os equipamentos,Tiro os aparelhos da tomada</t>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Embalagens de plástico</t>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão,Embalagens de plástico,Embalagens biodegradaveis/compostáveis</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+          <t>Nunca adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+          <t>As vezes reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -6963,134 +6963,5174 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
+        <v>46163.0</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Neusa Domingos</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>KHADYA AMADE SILIMO</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede,5.	Carvão</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2.	Algumas vezes por semana.</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro)</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="n">
         <v>46154.0</v>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Emilia Xavier</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>LATIZA AIUBA</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2.	Algumas vezes por semana.</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>O meu negócio não utiliza embalagens</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Nunca adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>46153.0</v>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Nampula</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>PAM VERDE</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Nelton Antonio Duarte</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de plástico</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>46199.0</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Beira</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Atija Baltazar Duarte</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Lúcia Vicente Francisco</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Embalagens de plástico</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>46199.0</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Beira</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Anabela Fernardo</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Luísa Gonçalo</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Embalagens de papel ou cartão,Embalagens biodegradaveis/compostáveis</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>46153.0</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Nelton Antonio Duarte</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>MADALENA CARIM MERAGE</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede,5.	Carvão,6.	Lenha,7.	Pilhas / baterias</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Compra sempre que precisa.</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão,Embalagens de plástico</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>As vezes reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>46163.0</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Faizela  Carlos</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>MARAVILHA JANUARIO  CARIA</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede,4.	Gás,5.	Carvão</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2.	Algumas vezes por semana.</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão,Embalagens de plástico</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>46199.0</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Beira</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Atija Baltazar Duarte</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Marcia Benedito Maculuve</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede,5.	Carvão</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2.	Algumas vezes por semana.</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Apago o fogão / carvão / lenha / gerador</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Embalagens de plástico</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Nunca adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>46199.0</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Beira</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Anabela Fernardo</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Maria José Alvaro Manuel</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2.	Algumas vezes por semana.</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Compra sempre que precisa.</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>O meu negócio não utiliza embalagens</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>As vezes reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>46155.0</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Nelton Antonio Duarte</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>MARIAMO  DOMINGOS JAIROSSE</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2.	Gerador,8.	Combustível (gasolina, diesel, petróleo)</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>4.	Raramente</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Apago o fogão / carvão / lenha / gerador,Guardo o combustível ou material de forma segura</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Compra sempre que precisa.</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de plástico,Embalagens biodegradaveis/compostáveis</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>Sempre utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>46156.0</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Emilia Xavier</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>MARIAMO HANIFA ABACAR CHALE SALIMO</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede,5.	Carvão</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Às vezes</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Deixo ligado porque ainda volto a usar</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Fora da cidade.</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro)</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Nunca adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Sempre utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>As vezes vende o lixo orgânico para compostagem.</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>46154.0</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Faizela  Carlos</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>MIMI IBRAIMO OMAR</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Compra sempre que precisa.</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>O meu negócio não utiliza embalagens</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>As vezes reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>46156.0</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Nelton Antonio Duarte</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>NATANIELA DILCIA MASSANGAIE</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>O meu negócio não utiliza embalagens</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>As vezes reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>46154.0</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cosme Militão</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>NGAMO SUMAIL</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede,4.	Gás,7.	Pilhas / baterias</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Guardo o combustível ou material de forma segura</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Embalagens de papel ou cartão,Embalagens de plástico</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>46197.0</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Beira</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Karina Sissa Machava</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Noemia Armindo Da Silva</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede,4.	Gás,5.	Carvão</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Embalagens de plástico</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>46157.0</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Nelton Antonio Duarte</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>OLINDA CARLINDO NAMIRECA</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede,4.	Gás,5.	Carvão,6.	Lenha</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2.	Algumas vezes por semana.</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão,Embalagens de plástico</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>Sempre utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>As vezes reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>As vezes reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>46155.0</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Faizela  Carlos</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>OTILIA LUIS</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede,5.	Carvão</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2.	Algumas vezes por semana.</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Compra sempre que precisa.</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Embalagens de papel ou cartão,Embalagens de plástico</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>As vezes utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>46199.0</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Beira</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Karina Sissa Machava</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Paula Julio Afonso Rassul</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede,4.	Gás</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador,Outro:</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Compra sempre que precisa.</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão,Embalagens de plástico</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>46154.0</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Faizela  Carlos</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>REGINA MANUEL PASSURI</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Compra sempre que precisa.</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>O meu negócio não utiliza embalagens</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>46197.0</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Beira</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Karina Sissa Machava</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Rosa Actassy</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Embalagens de papel ou cartão,Outro</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Take awey</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>As vezes reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="n">
+        <v>46156.0</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Cosme Militão</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>ROSA ERNESTO CASIMUCA</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede,4.	Gás,5.	Carvão</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador,Guardo o combustível ou material de forma segura</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Compra sempre que precisa.</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Embalagens de papel ou cartão,Embalagens de plástico</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>As vezes utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>46196.0</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Beira</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Karina Sissa Machava</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Rosa Muguio</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede,5.	Carvão</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Outro</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dentro do bairro e fora do bairro </t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Embalagens de plástico</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="n">
+        <v>46156.0</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Nelton Antonio Duarte</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>SAMIRA COMBO MUHOLE ASSUMANE</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2.	Algumas vezes por semana.</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Tiro os aparelhos da tomada</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Compra sempre que precisa.</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Embalagens de papel ou cartão,Embalagens biodegradaveis/compostáveis</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>As vezes separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>46197.0</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Beira</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Anabela Fernardo</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Sara João Valentim Pires</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>O meu negócio não utiliza embalagens</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Nunca adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>As vezes reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="n">
+        <v>46199.0</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Beira</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Atija Baltazar Duarte</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Shamim Alice Cardoso</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>4.	Gás,5.	Carvão</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Apago o fogão / carvão / lenha / gerador</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Outro</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alumínio </t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="n">
+        <v>46156.0</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
         <is>
           <t>Neusa Domingos</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>Ciclo 3</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>SHEILA MACARIO ANTONIO  CUMANRARE</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro)</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B76" s="1" t="n">
+        <v>46154.0</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Nelton Antonio Duarte</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>SHEILA RAIMUNDO ANTUNES</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede,7.	Pilhas / baterias,8.	Combustível (gasolina, diesel, petróleo)</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>3.	Algumas vezes por mês.</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Guardo o combustível ou material de forma segura</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Compra sempre que precisa.</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>O meu negócio não utiliza embalagens</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="n">
+        <v>46196.0</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Beira</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Atija Baltazar Duarte</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Shirley Mabjaia</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede,4.	Gás,5.	Carvão</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador,Guardo o combustível ou material de forma segura</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Embalagens de plástico</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="n">
+        <v>46196.0</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Beira</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Emilia Xavier</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Staube Madina Zilale</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>O meu negócio não utiliza embalagens</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="n">
+        <v>46156.0</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Cosme Militão</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>SUZANA JOAQUIM VAQUINA</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Guardo o combustível ou material de forma segura</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Embalagens de plástico</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>As vezes reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="n">
+        <v>46199.0</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Beira</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Karina Sissa Machava</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Tania de Jesus Silva Pedro Cabral</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2.	Algumas vezes por semana.</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Compra sempre que precisa.</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Outro</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Os clientes vem com seus plasticos e embalagens </t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B81" s="1" t="n">
+        <v>46155.0</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Neusa Domingos</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede,5.	Carvão</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Embalagens de plástico</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B82" s="1" t="n">
+        <v>46196.0</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Beira</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Karina Sissa Machava</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Teresa Manuel Herculano</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede,4.	Gás,5.	Carvão</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Fora da cidade.</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Compra a grosso 1-2 vezes na semana/mês (a depender do negocio)</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Embalagens reutilizáveis (ex: caixas, sacos de pano, frascos de vidro),Embalagens de papel ou cartão,Embalagens de plástico</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>As vezes utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="n">
+        <v>46157.0</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Faizela  Carlos</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>TUCHA OSVALDO FERNANDO</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>4.	Raramente</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Nunca</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Não faço nada em particular</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Compra dentro do meu bairro.</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Compra sempre que precisa.</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>O meu negócio não utiliza embalagens</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>As vezes adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Sempre utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B84" s="1" t="n">
+        <v>46156.0</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Faizela  Carlos</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>VIRGINIA ORLANDO AVELINO</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede,4.	Gás,5.	Carvão</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Compra sempre que precisa.</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>O meu negócio não utiliza embalagens</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Nunca separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B85" s="1" t="n">
+        <v>46154.0</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Faizela  Carlos</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>ZIBIA JOAO</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>1.	Eletricidade da rede,5.	Carvão</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>1.	Todos os dias.</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Sempre</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Desligo os equipamentos,Tiro os aparelhos da tomada</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Dentro da cidade (mas fora do bairro)</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Compra sempre que precisa.</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Embalagens de plástico</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>As vezes utiliza o lixo orgânico para a compostagem.</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>Nunca o lixo orgânico para compostagem</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza o lixo não orgânico dentro do negócio.</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B86" s="1" t="n">
+        <v>46154.0</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Neusa Domingos</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Ciclo 3</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
         <is>
           <t>ZINEIDE USSENE MARIO</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>1.	Eletricidade da rede,4.	Gás,5.	Carvão</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
+      <c r="L86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t>1.	Todos os dias.</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>Sempre</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>Desligo os equipamentos,Desligo as luzes,Tiro os aparelhos da tomada,Apago o fogão / carvão / lenha / gerador</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>Dentro da cidade (mas fora do bairro)</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
         <is>
           <t>Compra a grosso 3-4 vezes na semana/mês (a depender do negocio)</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>Embalagens de plástico</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
+      <c r="T86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
         <is>
           <t>Sempre adquire produtos vendidos em embalagens plásticas.</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
         <is>
           <t>Nunca utiliza meios de deslocação que tem baixa emissão de gases</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>Sempre separa o lixo orgânico do lixo não orgânico.</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Y86" t="inlineStr">
         <is>
           <t>Nunca utiliza o lixo orgânico para a compostagem.</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>Nunca o lixo orgânico para compostagem</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AA86" t="inlineStr">
         <is>
           <t>Sempre reutiliza o lixo não orgânico dentro do negócio.</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AB86" t="inlineStr">
         <is>
           <t>Nunca reutiliza agua para desempenhar atividades do negocio.</t>
         </is>
@@ -7357,13 +12397,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{634E77E5-2450-4F85-8E4A-92353F92EBB9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{482C6D38-3E48-461B-939A-6164662AA0F5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6530D6A6-8B96-4E2C-9A9F-23095B2911AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A571D4AC-D58A-46B3-BE3B-34C29FF6DC99}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C6E0CA3-4E20-4717-8D32-85783D39E7AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5E3D361-17AB-4C2F-8795-C0843FEA74C7}"/>
 </file>